--- a/Plots/Data.xlsx
+++ b/Plots/Data.xlsx
@@ -34,7 +34,7 @@
     <t xml:space="preserve">DDPM</t>
   </si>
   <si>
-    <t xml:space="preserve">CelebA-HQ</t>
+    <t xml:space="preserve">Train</t>
   </si>
   <si>
     <t xml:space="preserve">White</t>
@@ -55,6 +55,9 @@
     <t xml:space="preserve">Dataset</t>
   </si>
   <si>
+    <t xml:space="preserve">CelebA-HQ</t>
+  </si>
+  <si>
     <t xml:space="preserve">FairFace</t>
   </si>
   <si>
@@ -62,9 +65,6 @@
   </si>
   <si>
     <t xml:space="preserve">Bal-FairFace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bal - FairFace</t>
   </si>
   <si>
     <t xml:space="preserve">Male</t>
@@ -333,7 +333,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart123.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -436,7 +436,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -525,7 +525,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -614,7 +614,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -703,7 +703,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -732,12 +732,12 @@
         </c:ser>
         <c:gapWidth val="75"/>
         <c:shape val="box"/>
-        <c:axId val="96728682"/>
-        <c:axId val="12220482"/>
+        <c:axId val="72490978"/>
+        <c:axId val="88284339"/>
         <c:axId val="0"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="96728682"/>
+        <c:axId val="72490978"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -766,7 +766,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12220482"/>
+        <c:crossAx val="88284339"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -774,7 +774,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="12220482"/>
+        <c:axId val="88284339"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -808,7 +808,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96728682"/>
+        <c:crossAx val="72490978"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -851,7 +851,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart124.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -988,7 +988,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1077,7 +1077,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1166,7 +1166,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1255,7 +1255,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1284,12 +1284,12 @@
         </c:ser>
         <c:gapWidth val="79"/>
         <c:shape val="box"/>
-        <c:axId val="35024964"/>
-        <c:axId val="11306745"/>
+        <c:axId val="38268011"/>
+        <c:axId val="87855057"/>
         <c:axId val="0"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="35024964"/>
+        <c:axId val="38268011"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1321,7 +1321,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11306745"/>
+        <c:crossAx val="87855057"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1329,7 +1329,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11306745"/>
+        <c:axId val="87855057"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1395,7 +1395,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35024964"/>
+        <c:crossAx val="38268011"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1441,7 +1441,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart125.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1578,7 +1578,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1667,7 +1667,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1756,7 +1756,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1845,7 +1845,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1874,12 +1874,12 @@
         </c:ser>
         <c:gapWidth val="79"/>
         <c:shape val="box"/>
-        <c:axId val="9851283"/>
-        <c:axId val="27071000"/>
+        <c:axId val="54340766"/>
+        <c:axId val="77613840"/>
         <c:axId val="0"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="9851283"/>
+        <c:axId val="54340766"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1911,7 +1911,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27071000"/>
+        <c:crossAx val="77613840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1919,7 +1919,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="27071000"/>
+        <c:axId val="77613840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1985,7 +1985,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9851283"/>
+        <c:crossAx val="54340766"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2031,7 +2031,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart126.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2354,11 +2354,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="24037348"/>
-        <c:axId val="89531823"/>
+        <c:axId val="54655633"/>
+        <c:axId val="14753666"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="24037348"/>
+        <c:axId val="54655633"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2386,7 +2386,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89531823"/>
+        <c:crossAx val="14753666"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2394,7 +2394,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89531823"/>
+        <c:axId val="14753666"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2431,7 +2431,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24037348"/>
+        <c:crossAx val="54655633"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2479,7 +2479,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart127.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2548,7 +2548,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2633,7 +2633,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2718,7 +2718,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2803,7 +2803,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2832,11 +2832,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="24986213"/>
-        <c:axId val="83187806"/>
+        <c:axId val="40093921"/>
+        <c:axId val="24960815"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="24986213"/>
+        <c:axId val="40093921"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2864,7 +2864,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83187806"/>
+        <c:crossAx val="24960815"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2872,7 +2872,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83187806"/>
+        <c:axId val="24960815"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2909,7 +2909,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24986213"/>
+        <c:crossAx val="40093921"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2957,7 +2957,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart128.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -3026,7 +3026,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3111,7 +3111,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3196,7 +3196,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3281,7 +3281,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3310,11 +3310,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="27438313"/>
-        <c:axId val="36306352"/>
+        <c:axId val="76799667"/>
+        <c:axId val="76610159"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="27438313"/>
+        <c:axId val="76799667"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3342,7 +3342,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36306352"/>
+        <c:crossAx val="76610159"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3350,7 +3350,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36306352"/>
+        <c:axId val="76610159"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3387,7 +3387,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27438313"/>
+        <c:crossAx val="76799667"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3435,7 +3435,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart129.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -3504,7 +3504,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3589,7 +3589,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3674,7 +3674,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3759,7 +3759,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3788,11 +3788,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="70846497"/>
-        <c:axId val="5551451"/>
+        <c:axId val="96321127"/>
+        <c:axId val="59759576"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="70846497"/>
+        <c:axId val="96321127"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3820,7 +3820,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5551451"/>
+        <c:crossAx val="59759576"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3828,7 +3828,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="5551451"/>
+        <c:axId val="59759576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3865,7 +3865,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70846497"/>
+        <c:crossAx val="96321127"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3913,7 +3913,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart130.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -4016,7 +4016,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4105,7 +4105,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4134,12 +4134,12 @@
         </c:ser>
         <c:gapWidth val="79"/>
         <c:shape val="box"/>
-        <c:axId val="48732611"/>
-        <c:axId val="78486365"/>
+        <c:axId val="61081890"/>
+        <c:axId val="82680373"/>
         <c:axId val="0"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="48732611"/>
+        <c:axId val="61081890"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4171,7 +4171,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78486365"/>
+        <c:crossAx val="82680373"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4179,7 +4179,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78486365"/>
+        <c:axId val="82680373"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4245,7 +4245,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48732611"/>
+        <c:crossAx val="61081890"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4291,7 +4291,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart131.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -4394,7 +4394,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4483,7 +4483,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4512,12 +4512,12 @@
         </c:ser>
         <c:gapWidth val="79"/>
         <c:shape val="box"/>
-        <c:axId val="85277147"/>
-        <c:axId val="41515208"/>
+        <c:axId val="31633579"/>
+        <c:axId val="56000976"/>
         <c:axId val="0"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="85277147"/>
+        <c:axId val="31633579"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4549,7 +4549,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41515208"/>
+        <c:crossAx val="56000976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4557,7 +4557,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41515208"/>
+        <c:axId val="56000976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4623,7 +4623,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85277147"/>
+        <c:crossAx val="31633579"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4669,7 +4669,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart132.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -4772,7 +4772,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4861,7 +4861,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4890,12 +4890,12 @@
         </c:ser>
         <c:gapWidth val="79"/>
         <c:shape val="box"/>
-        <c:axId val="78150597"/>
-        <c:axId val="48943727"/>
+        <c:axId val="37098457"/>
+        <c:axId val="59074132"/>
         <c:axId val="0"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="78150597"/>
+        <c:axId val="37098457"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4927,7 +4927,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48943727"/>
+        <c:crossAx val="59074132"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4935,7 +4935,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48943727"/>
+        <c:axId val="59074132"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5001,7 +5001,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78150597"/>
+        <c:crossAx val="37098457"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5047,7 +5047,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart133.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -5116,7 +5116,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5201,7 +5201,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5230,11 +5230,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="81435856"/>
-        <c:axId val="97047557"/>
+        <c:axId val="72347820"/>
+        <c:axId val="21366310"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="81435856"/>
+        <c:axId val="72347820"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5262,7 +5262,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97047557"/>
+        <c:crossAx val="21366310"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5270,7 +5270,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97047557"/>
+        <c:axId val="21366310"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5307,7 +5307,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81435856"/>
+        <c:crossAx val="72347820"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5355,7 +5355,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart134.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -5424,7 +5424,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5509,7 +5509,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5538,11 +5538,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="23059701"/>
-        <c:axId val="99971477"/>
+        <c:axId val="99829792"/>
+        <c:axId val="75764122"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="23059701"/>
+        <c:axId val="99829792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5570,7 +5570,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99971477"/>
+        <c:crossAx val="75764122"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5578,7 +5578,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99971477"/>
+        <c:axId val="75764122"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5615,7 +5615,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23059701"/>
+        <c:crossAx val="99829792"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5663,7 +5663,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart135.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -5732,7 +5732,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5817,7 +5817,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5846,11 +5846,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="89413533"/>
-        <c:axId val="86747390"/>
+        <c:axId val="51417612"/>
+        <c:axId val="10302083"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="89413533"/>
+        <c:axId val="51417612"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5878,7 +5878,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86747390"/>
+        <c:crossAx val="10302083"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5886,7 +5886,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="86747390"/>
+        <c:axId val="10302083"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5923,7 +5923,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89413533"/>
+        <c:crossAx val="51417612"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5971,7 +5971,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart136.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -6294,11 +6294,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="83278437"/>
-        <c:axId val="55303120"/>
+        <c:axId val="99232556"/>
+        <c:axId val="74309607"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="83278437"/>
+        <c:axId val="99232556"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6326,7 +6326,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55303120"/>
+        <c:crossAx val="74309607"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6334,7 +6334,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55303120"/>
+        <c:axId val="74309607"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6371,7 +6371,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83278437"/>
+        <c:crossAx val="99232556"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6419,7 +6419,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart137.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -6522,7 +6522,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6611,7 +6611,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6700,7 +6700,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6789,7 +6789,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6878,7 +6878,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6967,7 +6967,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7056,7 +7056,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7085,12 +7085,12 @@
         </c:ser>
         <c:gapWidth val="79"/>
         <c:shape val="box"/>
-        <c:axId val="14622987"/>
-        <c:axId val="8674841"/>
+        <c:axId val="14276545"/>
+        <c:axId val="51145077"/>
         <c:axId val="0"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="14622987"/>
+        <c:axId val="14276545"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7122,7 +7122,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8674841"/>
+        <c:crossAx val="51145077"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7130,7 +7130,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8674841"/>
+        <c:axId val="51145077"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7196,7 +7196,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14622987"/>
+        <c:crossAx val="14276545"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7242,7 +7242,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart50.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart138.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -7345,7 +7345,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7434,7 +7434,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7523,7 +7523,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7612,7 +7612,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7701,7 +7701,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7790,7 +7790,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7879,7 +7879,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7968,7 +7968,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8057,7 +8057,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8086,12 +8086,12 @@
         </c:ser>
         <c:gapWidth val="79"/>
         <c:shape val="box"/>
-        <c:axId val="13083086"/>
-        <c:axId val="10106175"/>
+        <c:axId val="5129248"/>
+        <c:axId val="97168847"/>
         <c:axId val="0"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="13083086"/>
+        <c:axId val="5129248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8123,7 +8123,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10106175"/>
+        <c:crossAx val="97168847"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8131,7 +8131,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="10106175"/>
+        <c:axId val="97168847"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8197,7 +8197,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13083086"/>
+        <c:crossAx val="5129248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8243,7 +8243,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart139.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -8346,7 +8346,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8435,7 +8435,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8524,7 +8524,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8613,7 +8613,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8702,7 +8702,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8791,7 +8791,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8880,7 +8880,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8969,7 +8969,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9058,7 +9058,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9087,12 +9087,12 @@
         </c:ser>
         <c:gapWidth val="79"/>
         <c:shape val="box"/>
-        <c:axId val="60806087"/>
-        <c:axId val="66822711"/>
+        <c:axId val="53829216"/>
+        <c:axId val="37422640"/>
         <c:axId val="0"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="60806087"/>
+        <c:axId val="53829216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9124,7 +9124,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66822711"/>
+        <c:crossAx val="37422640"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9132,7 +9132,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66822711"/>
+        <c:axId val="37422640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9198,7 +9198,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60806087"/>
+        <c:crossAx val="53829216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9244,7 +9244,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart140.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -9567,11 +9567,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="99833276"/>
-        <c:axId val="11666431"/>
+        <c:axId val="41057794"/>
+        <c:axId val="5438135"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="99833276"/>
+        <c:axId val="41057794"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9599,7 +9599,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11666431"/>
+        <c:crossAx val="5438135"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9607,7 +9607,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11666431"/>
+        <c:axId val="5438135"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9644,7 +9644,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99833276"/>
+        <c:crossAx val="41057794"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9692,7 +9692,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart141.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -9761,7 +9761,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9846,7 +9846,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9931,7 +9931,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10016,7 +10016,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10101,7 +10101,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10186,7 +10186,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10271,7 +10271,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CelebA-HQ</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10300,11 +10300,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="89355930"/>
-        <c:axId val="94846966"/>
+        <c:axId val="18888085"/>
+        <c:axId val="17308811"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="89355930"/>
+        <c:axId val="18888085"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10332,7 +10332,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94846966"/>
+        <c:crossAx val="17308811"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10340,7 +10340,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94846966"/>
+        <c:axId val="17308811"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10377,7 +10377,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89355930"/>
+        <c:crossAx val="18888085"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10425,7 +10425,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart142.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -10494,7 +10494,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10579,7 +10579,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10664,7 +10664,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10749,7 +10749,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10834,7 +10834,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10919,7 +10919,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11004,7 +11004,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11089,7 +11089,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11174,7 +11174,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11203,11 +11203,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="21704859"/>
-        <c:axId val="60963912"/>
+        <c:axId val="83085861"/>
+        <c:axId val="97202994"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="21704859"/>
+        <c:axId val="83085861"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11235,7 +11235,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60963912"/>
+        <c:crossAx val="97202994"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11243,7 +11243,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60963912"/>
+        <c:axId val="97202994"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11280,7 +11280,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21704859"/>
+        <c:crossAx val="83085861"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11328,7 +11328,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart143.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -11397,7 +11397,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11482,7 +11482,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11567,7 +11567,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11652,7 +11652,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11737,7 +11737,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11822,7 +11822,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11907,7 +11907,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11992,7 +11992,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -12077,7 +12077,7 @@
                   <c:v>DDPM</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bal - FairFace</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -12106,11 +12106,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="13054246"/>
-        <c:axId val="41049737"/>
+        <c:axId val="12735518"/>
+        <c:axId val="55388242"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="13054246"/>
+        <c:axId val="12735518"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12138,7 +12138,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41049737"/>
+        <c:crossAx val="55388242"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12146,7 +12146,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41049737"/>
+        <c:axId val="55388242"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12183,7 +12183,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13054246"/>
+        <c:crossAx val="12735518"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12231,7 +12231,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart144.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -12786,11 +12786,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="54017909"/>
-        <c:axId val="78879299"/>
+        <c:axId val="13374022"/>
+        <c:axId val="11321420"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="54017909"/>
+        <c:axId val="13374022"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12822,7 +12822,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78879299"/>
+        <c:crossAx val="11321420"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12830,7 +12830,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78879299"/>
+        <c:axId val="11321420"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12869,7 +12869,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54017909"/>
+        <c:crossAx val="13374022"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12964,7 +12964,7 @@
       <xdr:col>20</xdr:col>
       <xdr:colOff>402120</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>81720</xdr:rowOff>
+      <xdr:rowOff>90720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12988,13 +12988,13 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>132120</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>57960</xdr:rowOff>
+      <xdr:rowOff>57600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>449280</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>119520</xdr:rowOff>
+      <xdr:rowOff>128520</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13002,7 +13002,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="10004760" y="5861520"/>
+        <a:off x="10004760" y="5852520"/>
         <a:ext cx="5633640" cy="2815200"/>
       </xdr:xfrm>
       <a:graphic>
@@ -13054,7 +13054,7 @@
       <xdr:col>28</xdr:col>
       <xdr:colOff>529560</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>128160</xdr:rowOff>
+      <xdr:rowOff>136800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13078,13 +13078,13 @@
       <xdr:col>21</xdr:col>
       <xdr:colOff>173520</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>146520</xdr:rowOff>
+      <xdr:rowOff>155520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>616680</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>80280</xdr:rowOff>
+      <xdr:rowOff>98280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13108,13 +13108,13 @@
       <xdr:col>21</xdr:col>
       <xdr:colOff>186120</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>36360</xdr:rowOff>
+      <xdr:rowOff>54000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>629280</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>145440</xdr:rowOff>
+      <xdr:rowOff>163080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13149,7 +13149,7 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>38880</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>70560</xdr:rowOff>
+      <xdr:rowOff>79200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13157,7 +13157,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6405480" y="260280"/>
+        <a:off x="6405480" y="251280"/>
         <a:ext cx="5784480" cy="2756520"/>
       </xdr:xfrm>
       <a:graphic>
@@ -13173,13 +13173,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>410760</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>83160</xdr:rowOff>
+      <xdr:rowOff>83520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>119520</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>121680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13187,7 +13187,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6486120" y="3582000"/>
+        <a:off x="6486120" y="3564360"/>
         <a:ext cx="5784480" cy="2756160"/>
       </xdr:xfrm>
       <a:graphic>
@@ -13217,7 +13217,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6544800" y="6522480"/>
+        <a:off x="6544800" y="6495840"/>
         <a:ext cx="5784480" cy="2756520"/>
       </xdr:xfrm>
       <a:graphic>
@@ -13233,13 +13233,13 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>206640</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:rowOff>54720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>649800</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>154800</xdr:rowOff>
+      <xdr:rowOff>172440</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13263,13 +13263,13 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>186120</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>152280</xdr:rowOff>
+      <xdr:rowOff>170280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>629280</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>113040</xdr:rowOff>
+      <xdr:rowOff>139680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13293,13 +13293,13 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>285840</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>32760</xdr:rowOff>
+      <xdr:rowOff>59400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>729000</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>141840</xdr:rowOff>
+      <xdr:rowOff>168480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13323,13 +13323,13 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>36360</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>36000</xdr:rowOff>
+      <xdr:rowOff>62640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>479880</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>180720</xdr:rowOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>23400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13356,15 +13356,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>319680</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>177480</xdr:rowOff>
+      <xdr:colOff>320040</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>236520</xdr:colOff>
+      <xdr:colOff>236880</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:rowOff>97920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13372,7 +13372,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="14749200" y="177480"/>
+        <a:off x="14749560" y="174960"/>
         <a:ext cx="11308680" cy="4333320"/>
       </xdr:xfrm>
       <a:graphic>
@@ -13386,15 +13386,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>319680</xdr:colOff>
+      <xdr:colOff>320040</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>72720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>233280</xdr:colOff>
+      <xdr:colOff>233640</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>148680</xdr:rowOff>
+      <xdr:rowOff>158040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13402,7 +13402,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="14749200" y="4860360"/>
+        <a:off x="14749560" y="4851720"/>
         <a:ext cx="11305440" cy="4127400"/>
       </xdr:xfrm>
       <a:graphic>
@@ -13416,15 +13416,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>334440</xdr:colOff>
+      <xdr:colOff>334800</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>101160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>279000</xdr:colOff>
+      <xdr:colOff>279360</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>85680</xdr:rowOff>
+      <xdr:rowOff>94680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13432,7 +13432,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="14763960" y="9124200"/>
+        <a:off x="14764320" y="9106560"/>
         <a:ext cx="11336400" cy="4035960"/>
       </xdr:xfrm>
       <a:graphic>
@@ -13448,13 +13448,13 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>36360</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>36000</xdr:rowOff>
+      <xdr:rowOff>62640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>479880</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>180720</xdr:rowOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13484,7 +13484,7 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>479880</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>145440</xdr:rowOff>
+      <xdr:rowOff>154080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13508,13 +13508,13 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>36360</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>36000</xdr:rowOff>
+      <xdr:rowOff>44640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>479880</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>145080</xdr:rowOff>
+      <xdr:rowOff>162720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13538,13 +13538,13 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>36360</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>114840</xdr:rowOff>
+      <xdr:rowOff>132480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>479880</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>48600</xdr:rowOff>
+      <xdr:rowOff>75240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>0.33</v>
@@ -13761,7 +13761,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>0.08</v>
@@ -13773,12 +13773,12 @@
         <v>0.12</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>0</v>
@@ -13790,10 +13790,10 @@
         <v>0.06</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
         <v>0</v>
       </c>
@@ -13804,7 +13804,7 @@
         <v>2</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13892,7 +13892,7 @@
         <v>7.77817459305202</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="1" t="s">
         <v>0</v>
       </c>
@@ -13903,7 +13903,7 @@
         <v>2</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14011,7 +14011,7 @@
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14077,7 +14077,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
         <v>0</v>
       </c>
@@ -14088,7 +14088,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14139,7 +14139,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="s">
         <v>0</v>
       </c>
@@ -14150,7 +14150,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14217,7 +14217,7 @@
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>0.14</v>
@@ -14234,7 +14234,7 @@
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>0.04</v>
@@ -14246,12 +14246,12 @@
         <v>0.06</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>0</v>
@@ -14263,7 +14263,7 @@
         <v>0.07</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -14286,7 +14286,7 @@
   <dimension ref="A1:E77"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14437,7 +14437,7 @@
         <v>20.0763847465074</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
         <v>0</v>
       </c>
@@ -14448,7 +14448,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14622,7 +14622,7 @@
         <v>10.3649456711279</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="1" t="s">
         <v>0</v>
       </c>
@@ -14633,7 +14633,7 @@
         <v>2</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14819,7 +14819,7 @@
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B75" s="1" t="n">
         <v>0.2</v>
@@ -14836,7 +14836,7 @@
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B76" s="0" t="n">
         <v>0.1</v>
@@ -14848,12 +14848,12 @@
         <v>0.15</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B77" s="0" t="n">
         <v>0.1</v>
@@ -14865,7 +14865,7 @@
         <v>0.12</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
